--- a/Termodinamica/p10_termodinamica/p10.xlsx
+++ b/Termodinamica/p10_termodinamica/p10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\proyectos\Termodinamica\p10_termodinamica\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andres\Practicas-Fisica\Termodinamica\p10_termodinamica\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEA461D-6E11-4AA2-AB11-F6978DC9F925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E2CC65-5C29-4F4A-BE3F-D0B095342D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Temperatura</t>
   </si>
@@ -50,25 +50,7 @@
     <t>u_Temperatura</t>
   </si>
   <si>
-    <t>Parte 1</t>
-  </si>
-  <si>
-    <t>t1</t>
-  </si>
-  <si>
-    <t>t2</t>
-  </si>
-  <si>
-    <t>r1</t>
-  </si>
-  <si>
-    <t>r2</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>OJO TODO EN KELVIN</t>
+    <t>celsius</t>
   </si>
 </sst>
 </file>
@@ -386,88 +368,222 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
-    <col min="2" max="2" width="32.21875" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <f>A2+273.15</f>
+        <v>278.14999999999998</v>
+      </c>
+      <c r="C2">
+        <v>0.1</v>
+      </c>
+      <c r="D2">
+        <v>25.25</v>
+      </c>
+      <c r="E2">
+        <f>D2*0.012+0.2</f>
+        <v>0.503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B2">
-        <f>0.1</f>
-        <v>0.1</v>
-      </c>
-      <c r="D2">
-        <f>0.1</f>
-        <v>0.1</v>
-      </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2">
-        <v>3</v>
-      </c>
-      <c r="L2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>3</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
+      <c r="B3">
+        <f>A3+273.15</f>
+        <v>283.14999999999998</v>
+      </c>
+      <c r="C3">
+        <v>0.1</v>
+      </c>
+      <c r="D3">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="E3">
+        <f>D3*0.012+0.2</f>
+        <v>0.43879999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <f t="shared" ref="B4:B11" si="0">A4+273.15</f>
+        <v>288.14999999999998</v>
+      </c>
+      <c r="C4">
+        <v>0.1</v>
+      </c>
+      <c r="D4">
+        <v>15.53</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E11" si="1">D4*0.012+0.2</f>
+        <v>0.38636000000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>293.14999999999998</v>
+      </c>
+      <c r="C5">
+        <v>0.1</v>
+      </c>
+      <c r="D5">
+        <v>12.26</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>0.34711999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>298.14999999999998</v>
+      </c>
+      <c r="C6">
+        <v>0.1</v>
+      </c>
+      <c r="D6">
+        <v>9.81</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>0.31772</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>30</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>303.14999999999998</v>
+      </c>
+      <c r="C7">
+        <v>0.1</v>
+      </c>
+      <c r="D7">
+        <v>7.8</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>0.29360000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>308.14999999999998</v>
+      </c>
+      <c r="C8">
+        <v>0.1</v>
+      </c>
+      <c r="D8">
+        <v>6.32</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>0.27584000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>40</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>313.14999999999998</v>
+      </c>
+      <c r="C9">
+        <v>0.1</v>
+      </c>
+      <c r="D9">
+        <v>5.13</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0.26156000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>45</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>318.14999999999998</v>
+      </c>
+      <c r="C10">
+        <v>0.1</v>
+      </c>
+      <c r="D10">
+        <v>4.2</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>0.25040000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>50</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>323.14999999999998</v>
+      </c>
+      <c r="C11">
+        <v>0.1</v>
+      </c>
+      <c r="D11">
+        <v>3.46</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>0.24152000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>